--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>143.0101</v>
+        <v>109.0217</v>
       </c>
       <c r="E2" t="n">
-        <v>88.6511</v>
+        <v>68.1571</v>
       </c>
       <c r="F2" t="n">
-        <v>54.3589</v>
+        <v>40.8642</v>
       </c>
       <c r="G2" t="n">
         <v>77.3657</v>
@@ -610,13 +610,13 @@
         <v>49.9894</v>
       </c>
       <c r="S2" t="n">
-        <v>61.272</v>
+        <v>27.2832</v>
       </c>
       <c r="T2" t="n">
-        <v>33.1468</v>
+        <v>12.6528</v>
       </c>
       <c r="U2" t="n">
-        <v>28.1251</v>
+        <v>14.6304</v>
       </c>
       <c r="V2" t="n">
         <v>11.321</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>81.0303</v>
+        <v>83.0005</v>
       </c>
       <c r="E3" t="n">
-        <v>50.4553</v>
+        <v>52.2138</v>
       </c>
       <c r="F3" t="n">
-        <v>30.5753</v>
+        <v>30.7864</v>
       </c>
       <c r="G3" t="n">
         <v>38.9118</v>
@@ -688,13 +688,13 @@
         <v>41.6899</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6203</v>
+        <v>7.5903</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3971999999999998</v>
+        <v>1.3615</v>
       </c>
       <c r="U3" t="n">
-        <v>6.0178</v>
+        <v>6.228899999999999</v>
       </c>
       <c r="V3" t="n">
         <v>36.6915</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>74.1523</v>
+        <v>80.0629</v>
       </c>
       <c r="E4" t="n">
-        <v>49.1773</v>
+        <v>65.61669999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>24.9749</v>
+        <v>14.4466</v>
       </c>
       <c r="G4" t="n">
-        <v>34.781</v>
+        <v>67.73090000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>25.4504</v>
+        <v>18.736</v>
       </c>
       <c r="I4" t="n">
-        <v>9.3307</v>
+        <v>48.9947</v>
       </c>
       <c r="J4" t="n">
-        <v>37.7027</v>
+        <v>76.39150000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>28.6603</v>
+        <v>24.1172</v>
       </c>
       <c r="L4" t="n">
-        <v>9.0426</v>
+        <v>52.2747</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9218</v>
+        <v>-8.661</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.2102</v>
+        <v>-5.3811</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2880999999999999</v>
+        <v>-3.2796</v>
       </c>
       <c r="P4" t="n">
-        <v>4.0529</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.4782</v>
+        <v>-34.7411</v>
       </c>
       <c r="R4" t="n">
-        <v>40.5316</v>
+        <v>35.3206</v>
       </c>
       <c r="S4" t="n">
-        <v>30.2062</v>
+        <v>-1.7587</v>
       </c>
       <c r="T4" t="n">
-        <v>16.7118</v>
+        <v>-0.4664000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>13.4944</v>
+        <v>-1.2925</v>
       </c>
       <c r="V4" t="n">
-        <v>5.111800000000001</v>
+        <v>13.5118</v>
       </c>
       <c r="W4" t="n">
-        <v>31.2414</v>
+        <v>24.4329</v>
       </c>
       <c r="X4" t="n">
-        <v>-26.1298</v>
+        <v>-10.9212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>67.279</v>
+        <v>62.1017</v>
       </c>
       <c r="E5" t="n">
-        <v>57.649</v>
+        <v>42.3465</v>
       </c>
       <c r="F5" t="n">
-        <v>9.6303</v>
+        <v>19.7551</v>
       </c>
       <c r="G5" t="n">
-        <v>67.73090000000001</v>
+        <v>44.592</v>
       </c>
       <c r="H5" t="n">
-        <v>18.736</v>
+        <v>24.1497</v>
       </c>
       <c r="I5" t="n">
-        <v>48.9947</v>
+        <v>20.4422</v>
       </c>
       <c r="J5" t="n">
-        <v>76.39150000000001</v>
+        <v>61.7844</v>
       </c>
       <c r="K5" t="n">
-        <v>24.1172</v>
+        <v>35.0988</v>
       </c>
       <c r="L5" t="n">
-        <v>52.2747</v>
+        <v>26.6851</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.661</v>
+        <v>-17.1922</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.3811</v>
+        <v>-10.9493</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.2796</v>
+        <v>-6.2428</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5790999999999999</v>
+        <v>11.1946</v>
       </c>
       <c r="Q5" t="n">
-        <v>-34.7411</v>
+        <v>-27.9859</v>
       </c>
       <c r="R5" t="n">
-        <v>35.3206</v>
+        <v>39.1807</v>
       </c>
       <c r="S5" t="n">
-        <v>-14.5422</v>
+        <v>9.0924</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.434100000000001</v>
+        <v>2.9478</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.1086</v>
+        <v>6.1449</v>
       </c>
       <c r="V5" t="n">
-        <v>13.5118</v>
+        <v>-2.7777</v>
       </c>
       <c r="W5" t="n">
-        <v>24.4329</v>
+        <v>5.6004</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.9212</v>
+        <v>-8.3781</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>56.7894</v>
+        <v>60.0633</v>
       </c>
       <c r="E6" t="n">
-        <v>36.6684</v>
+        <v>36.6249</v>
       </c>
       <c r="F6" t="n">
-        <v>20.121</v>
+        <v>23.4387</v>
       </c>
       <c r="G6" t="n">
         <v>28.9734</v>
@@ -922,13 +922,13 @@
         <v>46.7082</v>
       </c>
       <c r="S6" t="n">
-        <v>7.834</v>
+        <v>11.108</v>
       </c>
       <c r="T6" t="n">
-        <v>4.3249</v>
+        <v>4.281099999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>3.5092</v>
+        <v>6.8264</v>
       </c>
       <c r="V6" t="n">
         <v>1.4535</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>52.6376</v>
+        <v>58.0936</v>
       </c>
       <c r="E7" t="n">
-        <v>36.36</v>
+        <v>39.0381</v>
       </c>
       <c r="F7" t="n">
-        <v>16.2775</v>
+        <v>19.0554</v>
       </c>
       <c r="G7" t="n">
-        <v>44.592</v>
+        <v>34.781</v>
       </c>
       <c r="H7" t="n">
-        <v>24.1497</v>
+        <v>25.4504</v>
       </c>
       <c r="I7" t="n">
-        <v>20.4422</v>
+        <v>9.3307</v>
       </c>
       <c r="J7" t="n">
-        <v>61.7844</v>
+        <v>37.7027</v>
       </c>
       <c r="K7" t="n">
-        <v>35.0988</v>
+        <v>28.6603</v>
       </c>
       <c r="L7" t="n">
-        <v>26.6851</v>
+        <v>9.0426</v>
       </c>
       <c r="M7" t="n">
-        <v>-17.1922</v>
+        <v>-2.9218</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.9493</v>
+        <v>-3.2102</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.2428</v>
+        <v>0.2880999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>11.1946</v>
+        <v>4.0529</v>
       </c>
       <c r="Q7" t="n">
-        <v>-27.9859</v>
+        <v>-36.4782</v>
       </c>
       <c r="R7" t="n">
-        <v>39.1807</v>
+        <v>40.5316</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3715999999999997</v>
+        <v>14.1481</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.0387</v>
+        <v>6.5727</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6673</v>
+        <v>7.575</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7777</v>
+        <v>5.111800000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>5.6004</v>
+        <v>31.2414</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.3781</v>
+        <v>-26.1298</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>34.5242</v>
+        <v>38.4315</v>
       </c>
       <c r="E8" t="n">
-        <v>18.2159</v>
+        <v>19.5556</v>
       </c>
       <c r="F8" t="n">
-        <v>16.3082</v>
+        <v>18.8759</v>
       </c>
       <c r="G8" t="n">
         <v>17.9371</v>
@@ -1078,13 +1078,13 @@
         <v>37.6366</v>
       </c>
       <c r="S8" t="n">
-        <v>4.19</v>
+        <v>8.097099999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>3.0583</v>
+        <v>4.3979</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1316</v>
+        <v>3.6996</v>
       </c>
       <c r="V8" t="n">
         <v>3.3259</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>30.6128</v>
+        <v>36.6304</v>
       </c>
       <c r="E9" t="n">
-        <v>26.8494</v>
+        <v>11.7258</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7631</v>
+        <v>24.9045</v>
       </c>
       <c r="G9" t="n">
-        <v>27.3552</v>
+        <v>37.8551</v>
       </c>
       <c r="H9" t="n">
-        <v>11.823</v>
+        <v>10.6837</v>
       </c>
       <c r="I9" t="n">
-        <v>15.5321</v>
+        <v>27.1714</v>
       </c>
       <c r="J9" t="n">
-        <v>29.5214</v>
+        <v>37.7592</v>
       </c>
       <c r="K9" t="n">
-        <v>12.3727</v>
+        <v>12.4657</v>
       </c>
       <c r="L9" t="n">
-        <v>17.1487</v>
+        <v>25.294</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1662</v>
+        <v>0.09599999999999953</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5495999999999999</v>
+        <v>-1.7814</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6166</v>
+        <v>1.8777</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>7.7201</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.8083</v>
+        <v>-26.8278</v>
       </c>
       <c r="R9" t="n">
-        <v>11.3876</v>
+        <v>34.5482</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1489</v>
+        <v>0.1511000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9464</v>
+        <v>-1.3326</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2025</v>
+        <v>1.4835</v>
       </c>
       <c r="V9" t="n">
-        <v>4.8274</v>
+        <v>-9.096</v>
       </c>
       <c r="W9" t="n">
-        <v>9.0831</v>
+        <v>2.1279</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.2556</v>
+        <v>-11.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>26.3695</v>
+        <v>33.7324</v>
       </c>
       <c r="E10" t="n">
-        <v>4.300099999999999</v>
+        <v>28.4706</v>
       </c>
       <c r="F10" t="n">
-        <v>22.0699</v>
+        <v>5.2618</v>
       </c>
       <c r="G10" t="n">
-        <v>37.8551</v>
+        <v>27.3552</v>
       </c>
       <c r="H10" t="n">
-        <v>10.6837</v>
+        <v>11.823</v>
       </c>
       <c r="I10" t="n">
-        <v>27.1714</v>
+        <v>15.5321</v>
       </c>
       <c r="J10" t="n">
-        <v>37.7592</v>
+        <v>29.5214</v>
       </c>
       <c r="K10" t="n">
-        <v>12.4657</v>
+        <v>12.3727</v>
       </c>
       <c r="L10" t="n">
-        <v>25.294</v>
+        <v>17.1487</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09599999999999953</v>
+        <v>-2.1662</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7814</v>
+        <v>-0.5495999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8777</v>
+        <v>-1.6166</v>
       </c>
       <c r="P10" t="n">
-        <v>7.7201</v>
+        <v>0.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-26.8278</v>
+        <v>-10.8083</v>
       </c>
       <c r="R10" t="n">
-        <v>34.5482</v>
+        <v>11.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.1101</v>
+        <v>0.971</v>
       </c>
       <c r="T10" t="n">
-        <v>-8.7592</v>
+        <v>0.6746</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3507</v>
+        <v>0.2961000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-9.096</v>
+        <v>4.8274</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1279</v>
+        <v>9.0831</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.2239</v>
+        <v>-4.2556</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>23.4863</v>
+        <v>25.3358</v>
       </c>
       <c r="E11" t="n">
-        <v>9.832800000000001</v>
+        <v>9.2477</v>
       </c>
       <c r="F11" t="n">
-        <v>13.6534</v>
+        <v>16.0879</v>
       </c>
       <c r="G11" t="n">
         <v>27.8337</v>
@@ -1312,13 +1312,13 @@
         <v>35.8994</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3275</v>
+        <v>5.1768</v>
       </c>
       <c r="T11" t="n">
-        <v>4.0007</v>
+        <v>3.4159</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6732</v>
+        <v>1.761</v>
       </c>
       <c r="V11" t="n">
         <v>-9.9907</v>
@@ -1345,13 +1345,13 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>7.805400000000001</v>
+        <v>24.5611</v>
       </c>
       <c r="E12" t="n">
-        <v>4.601400000000001</v>
+        <v>13.9708</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2041</v>
+        <v>10.5898</v>
       </c>
       <c r="G12" t="n">
         <v>16.9712</v>
@@ -1390,13 +1390,13 @@
         <v>39.1808</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.7253</v>
+        <v>4.0303</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.559200000000001</v>
+        <v>0.8102999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1663</v>
+        <v>3.2196</v>
       </c>
       <c r="V12" t="n">
         <v>-9.9511</v>
@@ -1423,13 +1423,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6144</v>
+        <v>-3.5338</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4773999999999999</v>
+        <v>-0.8778999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1371</v>
+        <v>-2.656</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2783</v>
@@ -1468,13 +1468,13 @@
         <v>1.351</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06609999999999999</v>
+        <v>0.01440000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2787</v>
+        <v>-0.1216999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3452</v>
+        <v>0.1361</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4982</v>
@@ -1501,13 +1501,13 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.893199999999999</v>
+        <v>-3.797699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.8642</v>
+        <v>-6.5074</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9708999999999999</v>
+        <v>2.7095</v>
       </c>
       <c r="G14" t="n">
         <v>-6.6744</v>
@@ -1546,13 +1546,13 @@
         <v>15.0543</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4734</v>
+        <v>2.5687</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2454</v>
+        <v>1.6025</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7723</v>
+        <v>0.966</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7804</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>588.1892999999999</v>
+        <v>603.7034</v>
       </c>
       <c r="E15" t="n">
-        <v>375.4191000000001</v>
+        <v>379.5823</v>
       </c>
       <c r="F15" t="n">
-        <v>212.7704</v>
+        <v>224.1198</v>
       </c>
       <c r="G15" t="n">
         <v>413.3544000000001</v>
@@ -1609,31 +1609,31 @@
         <v>-110.0993</v>
       </c>
       <c r="N15" t="n">
-        <v>-77.4876</v>
+        <v>-77.48760000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-32.6117</v>
+        <v>-32.61169999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>62.727</v>
+        <v>62.72700000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-365.747</v>
+        <v>-365.7469999999999</v>
       </c>
       <c r="R15" t="n">
         <v>428.4783</v>
       </c>
       <c r="S15" t="n">
-        <v>72.9592</v>
+        <v>88.4727</v>
       </c>
       <c r="T15" t="n">
-        <v>32.6318</v>
+        <v>36.7964</v>
       </c>
       <c r="U15" t="n">
-        <v>40.32659999999999</v>
+        <v>51.675</v>
       </c>
       <c r="V15" t="n">
-        <v>39.14879999999999</v>
+        <v>39.14880000000001</v>
       </c>
       <c r="W15" t="n">
         <v>185.0857</v>
